--- a/年报提取数据.xlsx
+++ b/年报提取数据.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7590"/>
+    <workbookView windowWidth="14450" windowHeight="7590" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t>年份</t>
   </si>
@@ -57,6 +59,12 @@
   </si>
   <si>
     <t>总资产增长率(%)</t>
+  </si>
+  <si>
+    <t>利息保障倍数</t>
+  </si>
+  <si>
+    <t>销售净利率</t>
   </si>
 </sst>
 </file>
@@ -700,7 +708,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -760,6 +768,1116 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0841578947368421"/>
+          <c:y val="0.0509259259259259"/>
+          <c:w val="0.888210526315789"/>
+          <c:h val="0.898148148148148"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>销售净利率</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-6.59</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.51</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-25.82</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-14.07</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-37.41</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-27.69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="583523198"/>
+        <c:axId val="265262462"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet3!$A$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>年份</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref/>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet3!$A$2:$A$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="7"/>
+                      <c:pt idx="0">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet3!$A$2:$A$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="7"/>
+                      <c:pt idx="0">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="583523198"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="265262462"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="265262462"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="583523198"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10055">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3289300" y="812800"/>
+        <a:ext cx="4826000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1047,8 +2165,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="3" width="12.8181818181818" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1058,9 +2176,10 @@
     <col min="8" max="8" width="18.3636363636364" customWidth="1"/>
     <col min="9" max="9" width="20.6363636363636" customWidth="1"/>
     <col min="10" max="10" width="18.3636363636364" customWidth="1"/>
+    <col min="11" max="11" width="14.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,297 +2210,709 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2">
-        <v>2017</v>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>2019</v>
       </c>
       <c r="B2" s="3">
-        <v>6.53308766728456</v>
+        <v>2.27062873998491</v>
       </c>
       <c r="C2" s="3">
-        <v>4.95269023914151</v>
+        <v>1.77864183348098</v>
       </c>
       <c r="D2" s="3">
-        <v>9.73875048950898</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1.42840971757411</v>
+        <v>29.520096754525</v>
+      </c>
+      <c r="E2">
+        <v>2.17</v>
       </c>
       <c r="F2" s="3">
-        <v>0.843415208847355</v>
+        <v>1.50086777845912</v>
       </c>
       <c r="G2" s="3">
-        <v>39.5819507966691</v>
+        <v>46.4483351080438</v>
       </c>
       <c r="H2" s="3">
-        <v>-13.9238492799993</v>
+        <v>-2.7690166267817</v>
       </c>
       <c r="I2" s="3">
-        <v>36.1202042865773</v>
+        <v>107.753287097772</v>
       </c>
       <c r="J2" s="3">
-        <v>-6.19594550262478</v>
+        <v>21.2386335381085</v>
+      </c>
+      <c r="K2">
+        <v>-4.04</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2">
-        <v>2018</v>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2020</v>
       </c>
       <c r="B3" s="3">
-        <v>5.38463088589307</v>
+        <v>1.76595125894154</v>
       </c>
       <c r="C3" s="3">
-        <v>4.03115240901185</v>
+        <v>1.45682779613263</v>
       </c>
       <c r="D3" s="3">
-        <v>11.4880611124377</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1.63776795651934</v>
+        <v>45.1883534811828</v>
+      </c>
+      <c r="E3">
+        <v>2.72</v>
       </c>
       <c r="F3" s="3">
-        <v>0.719225148365836</v>
+        <v>2.82470069642499</v>
       </c>
       <c r="G3" s="3">
-        <v>47.9335866136339</v>
+        <v>37.3675637477026</v>
       </c>
       <c r="H3" s="3">
-        <v>-9.74365992469038</v>
+        <v>10.3947229752733</v>
       </c>
       <c r="I3" s="3">
-        <v>31.477159357585</v>
+        <v>110.824069230961</v>
       </c>
       <c r="J3" s="3">
-        <v>-8.5607481902028</v>
+        <v>52.977455800743</v>
+      </c>
+      <c r="K3" s="3">
+        <v>16.3647426270444</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2">
-        <v>2019</v>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>2021</v>
       </c>
       <c r="B4" s="3">
-        <v>2.27062873998491</v>
+        <v>2.35582067052163</v>
       </c>
       <c r="C4" s="3">
-        <v>1.77864183348098</v>
+        <v>1.86593297549763</v>
       </c>
       <c r="D4" s="3">
-        <v>29.520096754525</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2.37964780522887</v>
+        <v>31.4068228483403</v>
+      </c>
+      <c r="E4">
+        <v>1.56</v>
       </c>
       <c r="F4" s="3">
-        <v>1.50086777845912</v>
+        <v>2.23188486891927</v>
       </c>
       <c r="G4" s="3">
-        <v>46.4483351080438</v>
+        <v>37.7053170771223</v>
       </c>
       <c r="H4" s="3">
-        <v>-2.7690166267817</v>
+        <v>7.02015463394425</v>
       </c>
       <c r="I4" s="3">
-        <v>107.753287097772</v>
+        <v>-9.06718073516221</v>
       </c>
       <c r="J4" s="3">
-        <v>21.2386335381085</v>
+        <v>-15.1169641698902</v>
+      </c>
+      <c r="K4" s="3">
+        <v>30.2201579340343</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2">
-        <v>2020</v>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2022</v>
       </c>
       <c r="B5" s="3">
-        <v>1.76595125894154</v>
+        <v>1.63991325874364</v>
       </c>
       <c r="C5" s="3">
-        <v>1.45682779613263</v>
+        <v>1.1859914007239</v>
       </c>
       <c r="D5" s="3">
-        <v>45.1883534811828</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2.81709052501766</v>
+        <v>44.3508394860441</v>
+      </c>
+      <c r="E5">
+        <v>0.53</v>
       </c>
       <c r="F5" s="3">
-        <v>2.82470069642499</v>
+        <v>0.782179259059266</v>
       </c>
       <c r="G5" s="3">
-        <v>37.3675637477026</v>
+        <v>40.140456058168</v>
       </c>
       <c r="H5" s="3">
-        <v>10.3947229752733</v>
+        <v>-5.98272227684464</v>
       </c>
       <c r="I5" s="3">
-        <v>110.824069230961</v>
+        <v>-56.6206609997908</v>
       </c>
       <c r="J5" s="3">
-        <v>52.977455800743</v>
+        <v>11.871133074371</v>
+      </c>
+      <c r="K5" s="3">
+        <v>-16.0901505768008</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2">
-        <v>2021</v>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2023</v>
       </c>
       <c r="B6" s="3">
-        <v>2.35582067052163</v>
+        <v>1.81109902058914</v>
       </c>
       <c r="C6" s="3">
-        <v>1.86593297549763</v>
+        <v>1.15419358651468</v>
       </c>
       <c r="D6" s="3">
-        <v>31.4068228483403</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1.60956771318976</v>
+        <v>38.5071206691113</v>
+      </c>
+      <c r="E6">
+        <v>0.61</v>
       </c>
       <c r="F6" s="3">
-        <v>2.23188486891927</v>
+        <v>0.645015292484808</v>
       </c>
       <c r="G6" s="3">
-        <v>37.7053170771223</v>
+        <v>39.2438475195059</v>
       </c>
       <c r="H6" s="3">
-        <v>7.02015463394425</v>
+        <v>-3.35515690418711</v>
       </c>
       <c r="I6" s="3">
-        <v>-9.06718073516221</v>
+        <v>1.42770374795281</v>
       </c>
       <c r="J6" s="3">
-        <v>-15.1169641698902</v>
+        <v>-13.3971630897131</v>
+      </c>
+      <c r="K6" s="3">
+        <v>-5.59367583501232</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2">
-        <v>2022</v>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2024</v>
       </c>
       <c r="B7" s="3">
-        <v>1.63991325874364</v>
+        <v>1.58948865155138</v>
       </c>
       <c r="C7" s="3">
-        <v>1.1859914007239</v>
+        <v>0.980668712866036</v>
       </c>
       <c r="D7" s="3">
-        <v>44.3508394860441</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.55022512740455</v>
+        <v>41.5960283909105</v>
+      </c>
+      <c r="E7">
+        <v>0.68</v>
       </c>
       <c r="F7" s="3">
-        <v>0.782179259059266</v>
+        <v>0.614396446148571</v>
       </c>
       <c r="G7" s="3">
-        <v>40.140456058168</v>
+        <v>26.4881898280549</v>
       </c>
       <c r="H7" s="3">
-        <v>-5.98272227684464</v>
+        <v>-7.91364128521096</v>
       </c>
       <c r="I7" s="3">
-        <v>-56.6206609997908</v>
+        <v>-20.8351223330617</v>
       </c>
       <c r="J7" s="3">
-        <v>11.871133074371</v>
+        <v>-7.67169510145759</v>
+      </c>
+      <c r="K7" s="3">
+        <v>-12.2197960814459</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2">
-        <v>2023</v>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>2025</v>
       </c>
       <c r="B8" s="3">
-        <v>1.81109902058914</v>
+        <v>1.42405169758605</v>
       </c>
       <c r="C8" s="3">
-        <v>1.15419358651468</v>
+        <v>0.912139335762206</v>
       </c>
       <c r="D8" s="3">
-        <v>38.5071206691113</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.638924162024361</v>
+        <v>48.0564345201317</v>
+      </c>
+      <c r="E8">
+        <v>0.94</v>
       </c>
       <c r="F8" s="3">
-        <v>0.645015292484808</v>
+        <v>0.780663298044017</v>
       </c>
       <c r="G8" s="3">
-        <v>39.2438475195059</v>
+        <v>32.6250412840589</v>
       </c>
       <c r="H8" s="3">
-        <v>-3.35515690418711</v>
+        <v>-8.00926456348069</v>
       </c>
       <c r="I8" s="3">
-        <v>1.42770374795281</v>
+        <v>29.4432304090598</v>
       </c>
       <c r="J8" s="3">
-        <v>-13.3971630897131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1.58948865155138</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.980668712866036</v>
-      </c>
-      <c r="D9" s="3">
-        <v>41.5960283909105</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.731942878017957</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.614396446148571</v>
-      </c>
-      <c r="G9" s="3">
-        <v>26.4881898280549</v>
-      </c>
-      <c r="H9" s="3">
-        <v>-7.91364128521096</v>
-      </c>
-      <c r="I9" s="3">
-        <v>-20.8351223330617</v>
-      </c>
-      <c r="J9" s="3">
-        <v>-7.67169510145759</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B10" s="3">
-        <v>1.42405169758605</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.912139335762206</v>
-      </c>
-      <c r="D10" s="3">
-        <v>48.0564345201317</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1.03024847794551</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.780663298044017</v>
-      </c>
-      <c r="G10" s="3">
-        <v>32.6250412840589</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-8.00926456348069</v>
-      </c>
-      <c r="I10" s="3">
-        <v>29.4432304090598</v>
-      </c>
-      <c r="J10" s="3">
         <v>-2.84119769598423</v>
+      </c>
+      <c r="K8" s="3">
+        <v>-8.35414969453788</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="9"/>
+    <col min="2" max="2" width="12.8181818181818"/>
+    <col min="3" max="3" width="9.90909090909091" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14.6363636363636" customWidth="1"/>
+    <col min="6" max="6" width="21.8181818181818" customWidth="1"/>
+    <col min="7" max="7" width="17.0909090909091" customWidth="1"/>
+    <col min="8" max="8" width="11.2727272727273" customWidth="1"/>
+    <col min="9" max="9" width="18.3636363636364" customWidth="1"/>
+    <col min="10" max="10" width="20.6363636363636" customWidth="1"/>
+    <col min="11" max="11" width="18.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2">
+        <f>(Sheet1!B2-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>0.908569685178163</v>
+      </c>
+      <c r="C2">
+        <f>(Sheet1!C2-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>0.908480054405831</v>
+      </c>
+      <c r="D2">
+        <f>(Sheet1!D8-Sheet1!D2)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <f>(Sheet1!K2-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>0.260204497967908</v>
+      </c>
+      <c r="F2">
+        <f>(Sheet1!E2-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>0.748858447488584</v>
+      </c>
+      <c r="G2">
+        <f>(Sheet1!F2-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>0.401063035643029</v>
+      </c>
+      <c r="H2">
+        <f>(Sheet1!G2-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>(Sheet1!H2-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>0.284734377572491</v>
+      </c>
+      <c r="J2">
+        <f>(Sheet1!I2-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>0.981660921015805</v>
+      </c>
+      <c r="K2">
+        <f>(Sheet1!J2-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>0.533899807409735</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2020</v>
+      </c>
+      <c r="B3">
+        <f>(Sheet1!B3-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>0.366935980147869</v>
+      </c>
+      <c r="C3">
+        <f>(Sheet1!C3-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>0.571075794258302</v>
+      </c>
+      <c r="D3">
+        <f>(Sheet1!D8-Sheet1!D3)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>0.154727491223778</v>
+      </c>
+      <c r="E3">
+        <f>(Sheet1!K3-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>0.700813582277298</v>
+      </c>
+      <c r="F3">
+        <f>(Sheet1!E3-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f>(Sheet1!F3-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <f>(Sheet1!G3-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>0.545054846397077</v>
+      </c>
+      <c r="I3">
+        <f>(Sheet1!H3-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <f>(Sheet1!I3-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <f>(Sheet1!J3-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4">
+        <f>(Sheet1!B4-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <f>(Sheet1!C4-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <f>(Sheet1!D8-Sheet1!D4)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>0.898214732722662</v>
+      </c>
+      <c r="E4">
+        <f>(Sheet1!K4-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <f>(Sheet1!E4-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>0.470319634703196</v>
+      </c>
+      <c r="G4">
+        <f>(Sheet1!F4-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>0.731794467919255</v>
+      </c>
+      <c r="H4">
+        <f>(Sheet1!G4-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>0.561976232723775</v>
+      </c>
+      <c r="I4">
+        <f>(Sheet1!H4-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>0.816639283512712</v>
+      </c>
+      <c r="J4">
+        <f>(Sheet1!I4-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>0.283995084223291</v>
+      </c>
+      <c r="K4">
+        <f>(Sheet1!J4-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5">
+        <f>(Sheet1!B5-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>0.231668543842481</v>
+      </c>
+      <c r="C5">
+        <f>(Sheet1!C5-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>0.2871187786885</v>
+      </c>
+      <c r="D5">
+        <f>(Sheet1!D8-Sheet1!D5)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>0.19990977079427</v>
+      </c>
+      <c r="E5">
+        <f>(Sheet1!K5-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>(Sheet1!E5-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>(Sheet1!F5-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>0.0759093744174415</v>
+      </c>
+      <c r="H5">
+        <f>(Sheet1!G5-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>0.68397629569361</v>
+      </c>
+      <c r="I5">
+        <f>(Sheet1!H5-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>0.110114304433682</v>
+      </c>
+      <c r="J5">
+        <f>(Sheet1!I5-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>(Sheet1!J5-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>0.396333462505448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6">
+        <f>(Sheet1!B6-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>0.415389795373503</v>
+      </c>
+      <c r="C6">
+        <f>(Sheet1!C6-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>0.25378052512451</v>
+      </c>
+      <c r="D6">
+        <f>(Sheet1!D8-Sheet1!D6)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>0.515167233774662</v>
+      </c>
+      <c r="E6">
+        <f>(Sheet1!K6-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>0.226655254074428</v>
+      </c>
+      <c r="F6">
+        <f>(Sheet1!E6-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>0.0365296803652968</v>
+      </c>
+      <c r="G6">
+        <f>(Sheet1!F6-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>0.0138527744912981</v>
+      </c>
+      <c r="H6">
+        <f>(Sheet1!G6-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>0.639056355177896</v>
+      </c>
+      <c r="I6">
+        <f>(Sheet1!H6-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>0.252885829741693</v>
+      </c>
+      <c r="J6">
+        <f>(Sheet1!I6-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>0.346671792344545</v>
+      </c>
+      <c r="K6">
+        <f>(Sheet1!J6-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>0.0252561234961513</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7">
+        <f>(Sheet1!B7-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>0.177551473348714</v>
+      </c>
+      <c r="C7">
+        <f>(Sheet1!C7-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>0.0718492703755496</v>
+      </c>
+      <c r="D7">
+        <f>(Sheet1!D8-Sheet1!D7)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>0.348526565005099</v>
+      </c>
+      <c r="E7">
+        <f>(Sheet1!K7-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>0.0835743621627863</v>
+      </c>
+      <c r="F7">
+        <f>(Sheet1!E7-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="G7">
+        <f>(Sheet1!F7-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>(Sheet1!G7-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f>(Sheet1!H7-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>0.00519579129622709</v>
+      </c>
+      <c r="J7">
+        <f>(Sheet1!I7-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>0.213715526415277</v>
+      </c>
+      <c r="K7">
+        <f>(Sheet1!J7-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>0.109337432812314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8">
+        <f>(Sheet1!B8-Sheet1!B8)/(Sheet1!B4-Sheet1!B8)</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f>(Sheet1!C8-Sheet1!C8)/(Sheet1!C4-Sheet1!C8)</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>(Sheet1!D8-Sheet1!D8)/(Sheet1!D8-Sheet1!D2)</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>(Sheet1!K8-Sheet1!K5)/(Sheet1!K4-Sheet1!K5)</f>
+        <v>0.167047059953249</v>
+      </c>
+      <c r="F8">
+        <f>(Sheet1!E8-Sheet1!E5)/(Sheet1!E3-Sheet1!E5)</f>
+        <v>0.187214611872146</v>
+      </c>
+      <c r="G8">
+        <f>(Sheet1!F8-Sheet1!F7)/(Sheet1!F3-Sheet1!F7)</f>
+        <v>0.0752235136292448</v>
+      </c>
+      <c r="H8">
+        <f>(Sheet1!G8-Sheet1!G7)/(Sheet1!G2-Sheet1!G7)</f>
+        <v>0.307455249945326</v>
+      </c>
+      <c r="I8">
+        <f>(Sheet1!H8-Sheet1!H8)/(Sheet1!H3-Sheet1!H8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>(Sheet1!I8-Sheet1!I5)/(Sheet1!I3-Sheet1!I5)</f>
+        <v>0.513983875695866</v>
+      </c>
+      <c r="K8">
+        <f>(Sheet1!J8-Sheet1!J4)/(Sheet1!J3-Sheet1!J4)</f>
+        <v>0.180275659579744</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B2" s="2">
+        <v>-6.59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="2">
+        <v>16.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="2">
+        <v>13.51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2">
+        <v>-25.82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="2">
+        <v>-14.07</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2">
+        <v>-37.41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="2">
+        <v>-27.69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>